--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
   <si>
     <t>location</t>
   </si>
@@ -116,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +164,16 @@
       <sz val="11"/>
       <color indexed="17"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -287,7 +297,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -319,6 +329,8 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -735,8 +747,8 @@
       <c r="F2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="G2" s="29" t="s">
-        <v>16</v>
+      <c r="G2" s="31" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -758,7 +770,7 @@
       <c r="F3" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="32" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
   <si>
     <t>location</t>
   </si>
@@ -116,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +164,21 @@
       <sz val="11"/>
       <color indexed="17"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -297,7 +312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -331,6 +346,9 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -747,7 +765,7 @@
       <c r="F2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="34" t="s">
         <v>22</v>
       </c>
     </row>
@@ -770,7 +788,7 @@
       <c r="F3" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="35" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="23">
   <si>
     <t>location</t>
   </si>
@@ -116,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +164,26 @@
       <sz val="11"/>
       <color indexed="17"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="17"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -367,7 +387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -415,6 +435,10 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -831,7 +855,7 @@
       <c r="F2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="49" t="s">
         <v>22</v>
       </c>
     </row>
@@ -854,7 +878,7 @@
       <c r="F3" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="G3" s="46" t="s">
+      <c r="G3" s="50" t="s">
         <v>16</v>
       </c>
     </row>
